--- a/artfynd/A 25501-2025 artfynd.xlsx
+++ b/artfynd/A 25501-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125481030</v>
+        <v>125480926</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>110349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590648</v>
+        <v>590651</v>
       </c>
       <c r="R2" t="n">
-        <v>6430343</v>
+        <v>6430223</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Några få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +776,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125480926</v>
+        <v>125481030</v>
       </c>
       <c r="B3" t="n">
-        <v>110163</v>
+        <v>58001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,35 +811,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590651</v>
+        <v>590648</v>
       </c>
       <c r="R3" t="n">
-        <v>6430223</v>
+        <v>6430343</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,11 +883,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Några få.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +891,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,7 +912,7 @@
         <v>125480983</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 25501-2025 artfynd.xlsx
+++ b/artfynd/A 25501-2025 artfynd.xlsx
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125481030</v>
+        <v>125480983</v>
       </c>
       <c r="B3" t="n">
-        <v>58001</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,39 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -847,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590648</v>
+        <v>590633</v>
       </c>
       <c r="R3" t="n">
-        <v>6430343</v>
+        <v>6430303</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,6 +887,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125480983</v>
+        <v>125481030</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>58001</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,35 +918,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590633</v>
+        <v>590648</v>
       </c>
       <c r="R4" t="n">
-        <v>6430303</v>
+        <v>6430343</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1002,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25501-2025 artfynd.xlsx
+++ b/artfynd/A 25501-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125480926</v>
+        <v>125481030</v>
       </c>
       <c r="B2" t="n">
-        <v>110349</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,35 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590651</v>
+        <v>590648</v>
       </c>
       <c r="R2" t="n">
-        <v>6430223</v>
+        <v>6430343</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,11 +758,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Några få.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +766,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,231 +781,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>125480983</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>A 25501, Göltorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>590633</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6430303</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Västra Ed</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>125481030</v>
-      </c>
-      <c r="B4" t="n">
-        <v>58001</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>A 25501, Göltorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>590648</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6430343</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Västervik</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Västra Ed</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25501-2025 artfynd.xlsx
+++ b/artfynd/A 25501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125481030</v>
       </c>
       <c r="B2" t="n">
-        <v>58019</v>
+        <v>58020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25501-2025 artfynd.xlsx
+++ b/artfynd/A 25501-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125481030</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
